--- a/4_outputs/final/Table12.xlsx
+++ b/4_outputs/final/Table12.xlsx
@@ -417,298 +417,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sample Size</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Coverage gap (vs policy)</t>
+          <t>Segments</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Semantic gap (raw)</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Semantic gap (adjusted)</t>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Distinct docs</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Multi-parent units</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Mega-doc segments</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mega-SDGs</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>Original (per-SDG dedup)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.056 ± 0.002</t>
+          <t>408</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.417 ± 0.020</t>
+          <t>204</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.284 ± 0.015</t>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>One-per-parent (global dedup)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.056 ± 0.001</t>
+          <t>408</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.384 ± 0.015</t>
+          <t>204</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.245 ± 0.010</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>5,000</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.056 ± 0.001</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0.358 ± 0.009</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.213 ± 0.007</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>10,000</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.056 ± 0.001</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.350 ± 0.006</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.201 ± 0.004</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.056 ± 0.000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.344 ± 0.005</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.194 ± 0.003</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>50,000</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.056 ± 0.000</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.342 ± 0.003</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.189 ± 0.002</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>100,000</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>0.056 ± 0.000</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0.341 ± 0.003</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.188 ± 0.002</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>200,000</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>0.056 ± 0.000</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0.340 ± 0.002</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0.187 ± 0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>500,000</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>0.056 ± 0.000</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0.340 ± 0.001</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.187 ± 0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1,000,000</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>0.056 ± 0.000</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0.340 ± 0.001</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.187 ± 0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2,000,000</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>0.056 ± 0.000</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0.340 ± 0.000</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0.186 ± 0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Full corpus</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0.056</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0.340</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0.187</t>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
